--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2541,8 +2648,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2553,704 +2664,781 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아리랑 낭낭 — 민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">아리랑 낭낭</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 夾</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">캐</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 㳞</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞
 南</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="G6" s="15"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 㳞</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 夾</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="15"/>
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="H10" s="12"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">처</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 㳞</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞
 夾</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="G12" s="14"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 南</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">녀</t>
         </is>
       </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="H13" s="12"/>
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南
 無</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 南</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢
 無</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="H14" s="12"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 仲</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H15" s="12"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 夾</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢
 仲</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">슴</t>
         </is>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" ht="48" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="H16" s="12"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲
 夾</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">바</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="H17" s="12"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 ○</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="15"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I20" s="2"/>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I44" s="2"/>
@@ -2870,7 +2870,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="10"/>
@@ -2948,7 +2948,7 @@
       <c r="G8" s="9"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="9"/>

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2766,476 +2807,476 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아리랑 낭낭</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="8"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G4" s="23"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K4" s="9"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I5" s="12"/>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E5" s="23"/>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G5" s="25"/>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C6" s="26"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="26"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="26"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
+      <c r="K6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="18" t="inlineStr">
+      <c r="I7" s="22"/>
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K7" s="11"/>
+      <c r="K7" s="27"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="23"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="23"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E9" s="23"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G9" s="23"/>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="25"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E10" s="26"/>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G10" s="26"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K10" s="13"/>
+      <c r="K10" s="28"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="11"/>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="8"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="9"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E12" s="23"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="23"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K12" s="23"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="B13" s="21"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="B14" s="21"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲㴌</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="G14" s="28"/>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K15" s="8"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E15" s="22"/>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G15" s="27"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="B16" s="21"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K16" s="9"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K17" s="9"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E17" s="23"/>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="B18" s="21"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E18" s="26"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞仲</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -2790,22 +2790,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="29.14" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -2835,11 +2835,11 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="23"/>
@@ -2868,11 +2868,11 @@
       </c>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C5" s="23"/>
@@ -2884,13 +2884,13 @@
       <c r="E5" s="23"/>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G5" s="25"/>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="25"/>
@@ -2901,11 +2901,11 @@
       </c>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="26"/>
@@ -2934,11 +2934,11 @@
       </c>
       <c r="K6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C7" s="22"/>
@@ -2967,11 +2967,11 @@
       </c>
       <c r="K7" s="27"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -3000,11 +3000,11 @@
       </c>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="23"/>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="26"/>
@@ -3066,19 +3066,19 @@
       </c>
       <c r="K10" s="28"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="22"/>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="27"/>
@@ -3095,13 +3095,13 @@
       </c>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -3124,13 +3124,13 @@
       </c>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -3142,7 +3142,7 @@
       <c r="G13" s="23"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="23"/>
@@ -3153,13 +3153,13 @@
       </c>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="26"/>
@@ -3182,19 +3182,19 @@
       </c>
       <c r="K14" s="28"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="29.14" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G15" s="27"/>
@@ -3202,18 +3202,18 @@
       <c r="I15" s="22"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -3227,24 +3227,24 @@
       <c r="I16" s="23"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E17" s="23"/>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G17" s="25"/>
@@ -3252,18 +3252,18 @@
       <c r="I17" s="23"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="26"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E18" s="26"/>

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2825,15 +2848,15 @@
     <row r="3" ht="29.14" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="21"/>
-      <c r="G3" s="22"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="22"/>
+      <c r="I3" s="29"/>
       <c r="J3" s="21"/>
-      <c r="K3" s="22"/>
+      <c r="K3" s="29"/>
     </row>
     <row r="4" ht="29.14" customHeight="1">
       <c r="A4" s="0"/>
@@ -2842,31 +2865,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="23"/>
+      <c r="G4" s="30"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="30"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="30"/>
     </row>
     <row r="5" ht="29.14" customHeight="1">
       <c r="A5" s="0"/>
@@ -2875,31 +2898,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C5" s="23"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="30"/>
       <c r="F5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="25"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="23"/>
+      <c r="K5" s="30"/>
     </row>
     <row r="6" ht="29.14" customHeight="1">
       <c r="A6" s="0"/>
@@ -2908,31 +2931,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I6" s="26"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K6" s="26"/>
+      <c r="K6" s="32"/>
     </row>
     <row r="7" ht="29.14" customHeight="1">
       <c r="A7" s="0"/>
@@ -2941,31 +2964,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I7" s="22"/>
+      <c r="I7" s="29"/>
       <c r="J7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K7" s="27"/>
+      <c r="K7" s="33"/>
     </row>
     <row r="8" ht="29.14" customHeight="1">
       <c r="A8" s="0"/>
@@ -2974,31 +2997,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="30"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="23"/>
+      <c r="I8" s="30"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K8" s="23"/>
+      <c r="K8" s="30"/>
     </row>
     <row r="9" ht="29.14" customHeight="1">
       <c r="A9" s="0"/>
@@ -3007,31 +3030,31 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="30"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="23"/>
+      <c r="G9" s="30"/>
       <c r="H9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K9" s="23"/>
+      <c r="K9" s="30"/>
     </row>
     <row r="10" ht="29.14" customHeight="1">
       <c r="A10" s="0"/>
@@ -3040,243 +3063,243 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="26"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K10" s="28"/>
+      <c r="K10" s="34"/>
     </row>
     <row r="11" ht="29.14" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="22"/>
+      <c r="I11" s="29"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="22"/>
+      <c r="K11" s="29"/>
     </row>
     <row r="12" ht="29.14" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
-      <c r="C12" s="23"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="23"/>
+      <c r="E12" s="30"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="23"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="23"/>
+      <c r="I12" s="30"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="23"/>
+      <c r="K12" s="30"/>
     </row>
     <row r="13" ht="29.14" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="30"/>
     </row>
     <row r="14" ht="29.14" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲㴌</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K14" s="28"/>
+      <c r="K14" s="34"/>
     </row>
     <row r="15" ht="29.14" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
-      <c r="C15" s="22"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G15" s="27"/>
+      <c r="G15" s="33"/>
       <c r="H15" s="21"/>
-      <c r="I15" s="22"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K15" s="22"/>
+      <c r="K15" s="29"/>
     </row>
     <row r="16" ht="29.14" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
-      <c r="C16" s="23"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G16" s="23"/>
+      <c r="G16" s="30"/>
       <c r="H16" s="21"/>
-      <c r="I16" s="23"/>
+      <c r="I16" s="30"/>
       <c r="J16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K16" s="23"/>
+      <c r="K16" s="30"/>
     </row>
     <row r="17" ht="29.14" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
-      <c r="C17" s="23"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E17" s="23"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="31"/>
       <c r="H17" s="21"/>
-      <c r="I17" s="23"/>
+      <c r="I17" s="30"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K17" s="23"/>
+      <c r="K17" s="30"/>
     </row>
     <row r="18" ht="29.14" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
-      <c r="C18" s="26"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="32"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞仲</t>
         </is>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="21"/>
-      <c r="I18" s="26"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="21"/>
-      <c r="K18" s="26"/>
+      <c r="K18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,37 +221,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -349,7 +323,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">48</t>
         </is>
       </c>
     </row>
@@ -361,7 +335,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -385,7 +359,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -397,7 +371,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">비고 18%</t>
+          <t xml:space="preserve">박자 근사</t>
         </is>
       </c>
     </row>
@@ -425,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16정간 양식. 번호 2개가 한 칸(위=홀수, 아래=짝수 정간). 오른쪽 2~5줄에 내용, 1줄과 바깥(6~8)줄은 빈 칸. 2줄 가사 칸에 "봄 봄봄이 왔네 봄이 와", 3줄에 "나물 캐러 간다고/아장아장 들가네" 류 글귀가 보임. 이 곡은 1930년대 신(新)민요로 작사·작곡자가 있는 현대 창작곡이라 가사(저작권 보호 가능성) 전사는 보류하고 멜로디(율명·기호)만 옮김. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움).</t>
         </is>
       </c>
     </row>
@@ -606,22 +580,26 @@
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I2" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
       <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
@@ -641,22 +619,26 @@
         <v>1</v>
       </c>
       <c r="E3" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I3" s="2"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
@@ -676,22 +658,27 @@
         <v>1</v>
       </c>
       <c r="E4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄이</t>
+        </is>
+      </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
     </row>
@@ -711,27 +698,28 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청성 겹침</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|㴌</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왔네</t>
+        </is>
+      </c>
+      <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
     <row r="6">
@@ -750,22 +738,27 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
         <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
+          <t xml:space="preserve">㳞|㳞</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I6" s="2"/>
+          <t xml:space="preserve">㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄이</t>
+        </is>
+      </c>
       <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
@@ -785,19 +778,20 @@
         <v>1</v>
       </c>
       <c r="E7" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
         <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–
+㴌</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -820,27 +814,27 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청성 겹침</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와</t>
+        </is>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
     <row r="9">
@@ -859,19 +853,20 @@
         <v>1</v>
       </c>
       <c r="E9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -894,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -909,7 +904,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫</t>
+        </is>
+      </c>
       <c r="J10" s="4"/>
       <c r="K10" s="2"/>
     </row>
@@ -929,23 +928,27 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="4"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선 하나(–/·?)</t>
+        </is>
+      </c>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -964,27 +967,28 @@
         <v>1</v>
       </c>
       <c r="E12" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2">
         <v>3</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청성 겹침</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|南</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+南</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처</t>
+        </is>
+      </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13">
@@ -1003,22 +1007,27 @@
         <v>1</v>
       </c>
       <c r="E13" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">無^|潢</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
+          <t xml:space="preserve">無^
+潢</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녀의</t>
+        </is>
+      </c>
       <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
@@ -1038,22 +1047,27 @@
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">無^|無^</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
+          <t xml:space="preserve">無^
+無^</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가슴</t>
+        </is>
+      </c>
       <c r="J14" s="4"/>
       <c r="K14" s="2"/>
     </row>
@@ -1073,22 +1087,27 @@
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2">
         <v>4</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
@@ -1102,28 +1121,32 @@
         </is>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I16" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1137,33 +1160,30 @@
         </is>
       </c>
       <c r="C17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응(점) 표시</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1182,22 +1202,27 @@
         <v>2</v>
       </c>
       <c r="E18" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나물</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1217,22 +1242,27 @@
         <v>2</v>
       </c>
       <c r="E19" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌|㴌</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I19" s="2"/>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐러</t>
+        </is>
+      </c>
       <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
@@ -1252,22 +1282,27 @@
         <v>2</v>
       </c>
       <c r="E20" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">㳞|–㴌</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I20" s="2"/>
+          <t xml:space="preserve">㳞
+–㴌</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간다</t>
+        </is>
+      </c>
       <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
@@ -1287,25 +1322,29 @@
         <v>2</v>
       </c>
       <c r="E21" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="I21" s="3"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">청성 겹침</t>
+          <t xml:space="preserve">가사 칸 아래 경계에 &lt; 표시</t>
         </is>
       </c>
       <c r="K21" s="2"/>
@@ -1326,22 +1365,27 @@
         <v>2</v>
       </c>
       <c r="E22" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아장</t>
+        </is>
+      </c>
       <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
@@ -1361,22 +1405,27 @@
         <v>2</v>
       </c>
       <c r="E23" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아장</t>
+        </is>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1396,22 +1445,27 @@
         <v>2</v>
       </c>
       <c r="E24" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㳞|㳞㴌</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
+          <t xml:space="preserve">㳞
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들로</t>
+        </is>
+      </c>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1431,23 +1485,31 @@
         <v>2</v>
       </c>
       <c r="E25" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2">
-        <v>3</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가네</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 아래 경계에 &lt; 표시</t>
+        </is>
+      </c>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1466,22 +1528,27 @@
         <v>2</v>
       </c>
       <c r="E26" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F26" s="2">
         <v>3</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">湳|湳</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
+          <t xml:space="preserve">湳
+湳</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산들</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1495,29 +1562,37 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산들</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">위에 덧써 지운 글자 있음</t>
+        </is>
+      </c>
       <c r="K27" s="2"/>
     </row>
     <row r="28">
@@ -1530,33 +1605,34 @@
         </is>
       </c>
       <c r="C28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응(점) 표시</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㳞㴌</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부는</t>
+        </is>
+      </c>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1569,28 +1645,33 @@
         </is>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
+          <t xml:space="preserve">潢|㴌</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바람</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1604,28 +1685,33 @@
         </is>
       </c>
       <c r="C30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無^|無潢</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I30" s="2"/>
+          <t xml:space="preserve">無^
+無潢</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리랑</t>
+        </is>
+      </c>
       <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
@@ -1639,29 +1725,38 @@
         </is>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F31" s="2">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢|無姑</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+無姑</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타령이</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 타/라?</t>
+        </is>
+      </c>
       <c r="K31" s="2"/>
     </row>
     <row r="32">
@@ -1674,28 +1769,33 @@
         </is>
       </c>
       <c r="C32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F32" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">仲|仲姑</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I32" s="2"/>
+          <t xml:space="preserve">仲
+仲姑</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절로</t>
+        </is>
+      </c>
       <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
@@ -1709,16 +1809,16 @@
         </is>
       </c>
       <c r="C33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -1730,7 +1830,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I33" s="2"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난다</t>
+        </is>
+      </c>
       <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
@@ -1750,27 +1854,27 @@
         <v>3</v>
       </c>
       <c r="E34" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I34" s="3"/>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응(점) 표시</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1789,19 +1893,20 @@
         <v>3</v>
       </c>
       <c r="E35" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+姑</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1824,22 +1929,26 @@
         <v>3</v>
       </c>
       <c r="E36" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
@@ -1859,27 +1968,24 @@
         <v>3</v>
       </c>
       <c r="E37" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
-        <v>3</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲㴌</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲㴌</t>
-        </is>
-      </c>
-      <c r="I37" s="3"/>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">청성 겹침</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|㴌</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="4"/>
       <c r="K37" s="2"/>
     </row>
     <row r="38">
@@ -1898,27 +2004,27 @@
         <v>3</v>
       </c>
       <c r="E38" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
-        <v>4</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I38" s="3"/>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응(점) 표시</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="J38" s="4"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39">
@@ -1937,19 +2043,20 @@
         <v>3</v>
       </c>
       <c r="E39" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">–
+湳</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -1972,27 +2079,27 @@
         <v>3</v>
       </c>
       <c r="E40" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
-        <v>4</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">응(점) 표시</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
     <row r="41">
@@ -2011,22 +2118,27 @@
         <v>3</v>
       </c>
       <c r="E41" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞仲</t>
+          <t xml:space="preserve">㳞㴌|㳞㴌</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞仲</t>
-        </is>
-      </c>
-      <c r="I41" s="2"/>
+          <t xml:space="preserve">㳞㴌
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2040,28 +2152,32 @@
         </is>
       </c>
       <c r="C42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J42" s="4"/>
       <c r="K42" s="2"/>
     </row>
@@ -2075,25 +2191,26 @@
         </is>
       </c>
       <c r="C43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D43" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F43" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">△|㴌</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">△
+㴌</t>
         </is>
       </c>
       <c r="I43" s="2"/>
@@ -2110,28 +2227,32 @@
         </is>
       </c>
       <c r="C44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I44" s="2"/>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
@@ -2145,28 +2266,33 @@
         </is>
       </c>
       <c r="C45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">無潢|無姑</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I45" s="2"/>
+          <t xml:space="preserve">無潢
+無姑</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J45" s="4"/>
       <c r="K45" s="2"/>
     </row>
@@ -2180,33 +2306,33 @@
         </is>
       </c>
       <c r="C46" s="2">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2">
+        <v>3</v>
+      </c>
+      <c r="E46" s="2">
+        <v>13</v>
+      </c>
+      <c r="F46" s="2">
         <v>4</v>
       </c>
-      <c r="D46" s="2">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>6</v>
-      </c>
-      <c r="F46" s="2">
-        <v>2</v>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I46" s="3"/>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세모 쉼</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2219,28 +2345,33 @@
         </is>
       </c>
       <c r="C47" s="2">
+        <v>3</v>
+      </c>
+      <c r="D47" s="2">
+        <v>3</v>
+      </c>
+      <c r="E47" s="2">
+        <v>14</v>
+      </c>
+      <c r="F47" s="2">
         <v>4</v>
       </c>
-      <c r="D47" s="2">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2">
-        <v>7</v>
-      </c>
-      <c r="F47" s="2">
-        <v>2</v>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|姑</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I47" s="2"/>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="J47" s="4"/>
       <c r="K47" s="2"/>
     </row>
@@ -2254,29 +2385,37 @@
         </is>
       </c>
       <c r="C48" s="2">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2">
+        <v>3</v>
+      </c>
+      <c r="E48" s="2">
+        <v>15</v>
+      </c>
+      <c r="F48" s="2">
         <v>4</v>
       </c>
-      <c r="D48" s="2">
-        <v>4</v>
-      </c>
-      <c r="E48" s="2">
-        <v>8</v>
-      </c>
-      <c r="F48" s="2">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I48" s="2"/>
-      <c r="J48" s="4"/>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">덧써 지운 흔적, 仲?</t>
+        </is>
+      </c>
       <c r="K48" s="2"/>
     </row>
     <row r="49">
@@ -2289,523 +2428,38 @@
         </is>
       </c>
       <c r="C49" s="2">
+        <v>3</v>
+      </c>
+      <c r="D49" s="2">
+        <v>3</v>
+      </c>
+      <c r="E49" s="2">
+        <v>16</v>
+      </c>
+      <c r="F49" s="2">
         <v>4</v>
       </c>
-      <c r="D49" s="2">
-        <v>4</v>
-      </c>
-      <c r="E49" s="2">
-        <v>9</v>
-      </c>
-      <c r="F49" s="2">
-        <v>3</v>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="4"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="3"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">번짐</t>
+        </is>
+      </c>
       <c r="K49" s="2"/>
     </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>1</v>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C50" s="2">
-        <v>4</v>
-      </c>
-      <c r="D50" s="2">
-        <v>4</v>
-      </c>
-      <c r="E50" s="2">
-        <v>10</v>
-      </c>
-      <c r="F50" s="2">
-        <v>3</v>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I50" s="2"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>1</v>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C51" s="2">
-        <v>4</v>
-      </c>
-      <c r="D51" s="2">
-        <v>4</v>
-      </c>
-      <c r="E51" s="2">
-        <v>11</v>
-      </c>
-      <c r="F51" s="2">
-        <v>3</v>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I51" s="2"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>1</v>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C52" s="2">
-        <v>4</v>
-      </c>
-      <c r="D52" s="2">
-        <v>4</v>
-      </c>
-      <c r="E52" s="2">
-        <v>12</v>
-      </c>
-      <c r="F52" s="2">
-        <v>3</v>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I52" s="2"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>1</v>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C53" s="2">
-        <v>4</v>
-      </c>
-      <c r="D53" s="2">
-        <v>4</v>
-      </c>
-      <c r="E53" s="2">
-        <v>13</v>
-      </c>
-      <c r="F53" s="2">
-        <v>4</v>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I53" s="2"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>1</v>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C54" s="2">
-        <v>4</v>
-      </c>
-      <c r="D54" s="2">
-        <v>4</v>
-      </c>
-      <c r="E54" s="2">
-        <v>14</v>
-      </c>
-      <c r="F54" s="2">
-        <v>4</v>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2">
-        <v>1</v>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C55" s="2">
-        <v>4</v>
-      </c>
-      <c r="D55" s="2">
-        <v>4</v>
-      </c>
-      <c r="E55" s="2">
-        <v>15</v>
-      </c>
-      <c r="F55" s="2">
-        <v>4</v>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I55" s="2"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2">
-        <v>1</v>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C56" s="2">
-        <v>4</v>
-      </c>
-      <c r="D56" s="2">
-        <v>4</v>
-      </c>
-      <c r="E56" s="2">
-        <v>16</v>
-      </c>
-      <c r="F56" s="2">
-        <v>4</v>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>1</v>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C57" s="2">
-        <v>5</v>
-      </c>
-      <c r="D57" s="2">
-        <v>5</v>
-      </c>
-      <c r="E57" s="2">
-        <v>2</v>
-      </c>
-      <c r="F57" s="2">
-        <v>1</v>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I57" s="2"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2">
-        <v>1</v>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C58" s="2">
-        <v>5</v>
-      </c>
-      <c r="D58" s="2">
-        <v>5</v>
-      </c>
-      <c r="E58" s="2">
-        <v>3</v>
-      </c>
-      <c r="F58" s="2">
-        <v>1</v>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>1</v>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C59" s="2">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2">
-        <v>5</v>
-      </c>
-      <c r="E59" s="2">
-        <v>4</v>
-      </c>
-      <c r="F59" s="2">
-        <v>1</v>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>1</v>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C60" s="2">
-        <v>5</v>
-      </c>
-      <c r="D60" s="2">
-        <v>5</v>
-      </c>
-      <c r="E60" s="2">
-        <v>5</v>
-      </c>
-      <c r="F60" s="2">
-        <v>2</v>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>1</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C61" s="2">
-        <v>5</v>
-      </c>
-      <c r="D61" s="2">
-        <v>5</v>
-      </c>
-      <c r="E61" s="2">
-        <v>6</v>
-      </c>
-      <c r="F61" s="2">
-        <v>2</v>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2">
-        <v>1</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C62" s="2">
-        <v>5</v>
-      </c>
-      <c r="D62" s="2">
-        <v>5</v>
-      </c>
-      <c r="E62" s="2">
-        <v>7</v>
-      </c>
-      <c r="F62" s="2">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>1</v>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/아리랑 낭낭.png</t>
-        </is>
-      </c>
-      <c r="C63" s="2">
-        <v>5</v>
-      </c>
-      <c r="D63" s="2">
-        <v>5</v>
-      </c>
-      <c r="E63" s="2">
-        <v>8</v>
-      </c>
-      <c r="F63" s="2">
-        <v>2</v>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I63" s="2"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K63"/>
+  <autoFilter ref="A1:K49"/>
 </worksheet>
 </file>
 
@@ -2819,16 +2473,12 @@
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="29.14" customHeight="1">
+    <row r="2" ht="59.7" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2840,470 +2490,554 @@
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-    </row>
-    <row r="3" ht="29.14" customHeight="1">
+    </row>
+    <row r="3" ht="59.7" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" ht="29.14" customHeight="1">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+물</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="59.7" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C4" s="30"/>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="C4" s="23"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E4" s="30"/>
+          <t xml:space="preserve">㴌
+㴌</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">캐
+러</t>
+        </is>
+      </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="30"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K4" s="30"/>
-    </row>
-    <row r="5" ht="29.14" customHeight="1">
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="59.7" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C5" s="30"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="30"/>
-    </row>
-    <row r="6" ht="29.14" customHeight="1">
+          <t xml:space="preserve">㳞
+–㴌</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간
+다</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄
+이</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="59.7" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E6" s="32"/>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I6" s="32"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" ht="29.14" customHeight="1">
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">왔
+네</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="59.7" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C7" s="29"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E7" s="29"/>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+장</t>
+        </is>
+      </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="29"/>
-      <c r="J7" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="K7" s="33"/>
-    </row>
-    <row r="8" ht="29.14" customHeight="1">
+          <t xml:space="preserve">㳞
+㳞</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">봄
+이</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="59.7" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="E8" s="31"/>
+          <t xml:space="preserve">–
+湳</t>
+        </is>
+      </c>
+      <c r="C8" s="23"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+湳</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+장</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕</t>
-        </is>
-      </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I8" s="30"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="K8" s="30"/>
-    </row>
-    <row r="9" ht="29.14" customHeight="1">
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" ht="59.7" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C9" s="30"/>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="30"/>
+          <t xml:space="preserve">㳞
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들
+로</t>
+        </is>
+      </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="I9" s="31"/>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="K9" s="30"/>
-    </row>
-    <row r="10" ht="29.14" customHeight="1">
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="59.7" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㳞㴌
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+네</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G10" s="24"/>
+    </row>
+    <row r="11" ht="59.7" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+湳</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산
+들</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">숫</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="59.7" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△
+㴌</t>
+        </is>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산
+들</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" ht="59.7" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㳞㴌</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부
+는</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+南</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">처</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="59.7" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+無姑</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+㴌</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">바
+람</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+潢</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">녀
+의</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="59.7" customHeight="1">
+      <c r="A15" s="0"/>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+無潢</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+리
+랑</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+無^</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+슴</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="59.7" customHeight="1">
+      <c r="A16" s="0"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+姑</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+無姑</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">타
+령
+이</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="59.7" customHeight="1">
+      <c r="A17" s="0"/>
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="K10" s="34"/>
-    </row>
-    <row r="11" ht="29.14" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">응</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+仲姑</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">절
+로</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="59.7" customHeight="1">
+      <c r="A18" s="0"/>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" ht="29.14" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="30"/>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="30"/>
-    </row>
-    <row r="13" ht="29.14" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="G13" s="30"/>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="K13" s="30"/>
-    </row>
-    <row r="14" ht="29.14" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲㴌</t>
-        </is>
-      </c>
-      <c r="G14" s="34"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰</t>
-        </is>
-      </c>
-      <c r="K14" s="34"/>
-    </row>
-    <row r="15" ht="29.14" customHeight="1">
-      <c r="A15" s="0"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K15" s="29"/>
-    </row>
-    <row r="16" ht="29.14" customHeight="1">
-      <c r="A16" s="0"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="G16" s="30"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K16" s="30"/>
-    </row>
-    <row r="17" ht="29.14" customHeight="1">
-      <c r="A17" s="0"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K17" s="30"/>
-    </row>
-    <row r="18" ht="29.14" customHeight="1">
-      <c r="A18" s="0"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E18" s="32"/>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">난
+다</t>
+        </is>
+      </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞仲</t>
-        </is>
-      </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -218,19 +218,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -335,7 +335,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -359,7 +359,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -371,7 +371,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">박자 근사</t>
+          <t xml:space="preserve">비고 19%, 박자 근사</t>
         </is>
       </c>
     </row>
@@ -399,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움).</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(번호 1~16, 굵은 선 4칸마다) 16정간 4/4. 인쇄 줄번호 1은 빈 줄이라 제외, 인쇄 2·3·4번 줄을 줄1~3으로 적음(5~8 빈 줄). 줄3 가사 칸에는 가사 대신 '응'만 반복(허밍/받는소리로 보임). 無 오른쪽 작은 점·꺾쇠는 ^ 로 적음. 왼쪽 여백에 곡명 '아리랑 낭낭 '자?모리''(자진모리로 보임, #부제는 기존대로 비움). 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -1898,19 +1898,23 @@
       <c r="F35" s="2">
         <v>1</v>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|姑</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="4"/>
+南</t>
+        </is>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南/姑?</t>
+        </is>
+      </c>
       <c r="K35" s="2"/>
     </row>
     <row r="36">
@@ -2277,23 +2281,27 @@
       <c r="F45" s="2">
         <v>3</v>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢|無姑</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無姑</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="J45" s="4"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑/南?</t>
+        </is>
+      </c>
       <c r="K45" s="2"/>
     </row>
     <row r="46">
@@ -2528,20 +2536,20 @@
     </row>
     <row r="4" ht="59.7" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-姑</t>
-        </is>
-      </c>
-      <c r="C4" s="23"/>
+南</t>
+        </is>
+      </c>
+      <c r="C4" s="24"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">캐
 러</t>
@@ -2552,7 +2560,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">봄</t>
         </is>
@@ -2565,7 +2573,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -2576,7 +2584,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">간
 다</t>
@@ -2588,7 +2596,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">봄
 이</t>
@@ -2603,13 +2611,13 @@
 㴌</t>
         </is>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="C6" s="26"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -2620,7 +2628,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">왔
 네</t>
@@ -2672,14 +2680,14 @@
 湳</t>
         </is>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 湳</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 장</t>
@@ -2691,7 +2699,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="25"/>
     </row>
     <row r="9" ht="59.7" customHeight="1">
       <c r="A9" s="0"/>
@@ -2700,7 +2708,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -2711,7 +2719,7 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들
 로</t>
@@ -2722,7 +2730,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -2736,17 +2744,17 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 네</t>
@@ -2758,7 +2766,7 @@
 △</t>
         </is>
       </c>
-      <c r="G10" s="24"/>
+      <c r="G10" s="26"/>
     </row>
     <row r="11" ht="59.7" customHeight="1">
       <c r="A11" s="0"/>
@@ -2803,24 +2811,24 @@
 㴌</t>
         </is>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">산
 들</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="24"/>
     </row>
     <row r="13" ht="59.7" customHeight="1">
       <c r="A13" s="0"/>
@@ -2829,7 +2837,7 @@
           <t xml:space="preserve">無^</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -2840,7 +2848,7 @@
 㳞㴌</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">부
 는</t>
@@ -2852,7 +2860,7 @@
 南</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">처</t>
         </is>
@@ -2860,13 +2868,13 @@
     </row>
     <row r="14" ht="59.7" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無姑</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -2877,7 +2885,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">바
 람</t>
@@ -2889,7 +2897,7 @@
 潢</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">녀
 의</t>
@@ -2942,18 +2950,18 @@
 姑</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無姑</t>
         </is>
       </c>
-      <c r="E16" s="27" t="inlineStr">
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">타
 령
@@ -2966,7 +2974,7 @@
 南</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -2974,12 +2982,12 @@
     </row>
     <row r="17" ht="59.7" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -2990,7 +2998,7 @@
 仲姑</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">절
 로</t>
@@ -3001,7 +3009,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3009,19 +3017,19 @@
     </row>
     <row r="18" ht="59.7" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">난
 다</t>
@@ -3033,7 +3041,7 @@
 △</t>
         </is>
       </c>
-      <c r="G18" s="24"/>
+      <c r="G18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -2470,6 +2470,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2480,10 +2483,10 @@
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="59.7" customHeight="1">
+    <row r="2" ht="66.67" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2496,7 +2499,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="59.7" customHeight="1">
+    <row r="3" ht="74.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2531,7 +2534,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="59.7" customHeight="1">
+    <row r="4" ht="74.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2563,7 +2566,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="59.7" customHeight="1">
+    <row r="5" ht="74.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2600,7 +2603,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="59.7" customHeight="1">
+    <row r="6" ht="74.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2632,7 +2635,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="59.7" customHeight="1">
+    <row r="7" ht="74.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2669,7 +2672,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="59.7" customHeight="1">
+    <row r="8" ht="74.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2698,7 +2701,7 @@
       </c>
       <c r="G8" s="25"/>
     </row>
-    <row r="9" ht="59.7" customHeight="1">
+    <row r="9" ht="74.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2733,7 +2736,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="59.7" customHeight="1">
+    <row r="10" ht="74.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2765,7 +2768,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" ht="59.7" customHeight="1">
+    <row r="11" ht="74.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2800,7 +2803,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="59.7" customHeight="1">
+    <row r="12" ht="74.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2827,7 +2830,7 @@
       </c>
       <c r="G12" s="24"/>
     </row>
-    <row r="13" ht="59.7" customHeight="1">
+    <row r="13" ht="74.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2863,7 +2866,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="59.7" customHeight="1">
+    <row r="14" ht="74.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -2901,7 +2904,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="59.7" customHeight="1">
+    <row r="15" ht="74.45" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2939,7 +2942,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="59.7" customHeight="1">
+    <row r="16" ht="74.45" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2977,7 +2980,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="59.7" customHeight="1">
+    <row r="17" ht="74.45" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="23" t="inlineStr">
         <is>
@@ -3012,7 +3015,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="59.7" customHeight="1">
+    <row r="18" ht="74.45" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="23" t="inlineStr">
         <is>
@@ -3046,6 +3049,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="60"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/아리랑 낭낭.xlsx
+++ b/sheets/민요/검수/아리랑 낭낭.xlsx
@@ -2475,11 +2475,11 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
